--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직원명단" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="직원명단" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'직원명단'!$A$3:$I$33</definedName>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -84,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -93,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -554,14 +559,12 @@
           <t>생산직(조립)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2021-09-04</t>
-        </is>
+      <c r="F4" s="4" t="n">
+        <v>45928</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2년</t>
+          <t>1년</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -601,14 +604,12 @@
           <t>통번역 지원</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>2024-02-08</t>
-        </is>
+      <c r="F5" s="4" t="n">
+        <v>45777</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1년</t>
+          <t>1년 6개월</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -477,6 +477,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,6 +534,16 @@
           <t>비자유형</t>
         </is>
       </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>정착체크리스트(내부용)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -577,6 +589,16 @@
           <t>F-2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>할랄 식단 준수 필요 (돼지고기·알코올 제외) — 회식/구내식당 메뉴 안내 시 참고</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -622,6 +644,12 @@
           <t>E-9</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -669,6 +697,16 @@
           <t>E-7</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>글루텐 프리 식단 선호</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -716,6 +754,12 @@
           <t>F-2</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -763,6 +807,12 @@
           <t>F-4</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -810,6 +860,16 @@
           <t>D-8</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>특정 갑각류 알레르기 있음 — 회식 장소 선정 시 참고</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -857,6 +917,12 @@
           <t>D-8</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -904,6 +970,12 @@
           <t>E-7</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -951,6 +1023,16 @@
           <t>F-2</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>라마단 기간 중 근무시간 조정 요청 이력 있음 (2025년 3월)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -998,6 +1080,12 @@
           <t>E-9</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1045,6 +1133,12 @@
           <t>D-10</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1092,6 +1186,16 @@
           <t>E-7</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>GHD 내부 메모: 이전 소속사에서 임금 관련 민원 이력 있어 문의 응대 시 신중하게 접근</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1139,6 +1243,12 @@
           <t>D-10</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1186,6 +1296,12 @@
           <t>F-4</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1233,6 +1349,16 @@
           <t>E-9</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>채식(비건) 식단 선호</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1280,6 +1406,12 @@
           <t>F-2</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1327,6 +1459,12 @@
           <t>H-2</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1374,6 +1512,12 @@
           <t>E-9</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1421,6 +1565,16 @@
           <t>E-7</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>GHD 내부 메모: 한국어 의사소통에 다소 어려움 있어 안내 시 쉬운 표현 사용 권장</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1468,6 +1622,12 @@
           <t>E-7</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1515,6 +1675,12 @@
           <t>D-10</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1562,6 +1728,12 @@
           <t>D-10</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1609,6 +1781,12 @@
           <t>E-9</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1656,6 +1834,16 @@
           <t>F-2</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>힌두교 식습관상 소고기 제외 희망</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1703,6 +1891,12 @@
           <t>E-7</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1750,6 +1944,12 @@
           <t>F-2</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1797,6 +1997,12 @@
           <t>D-8</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1844,6 +2050,12 @@
           <t>E-9</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1891,6 +2103,12 @@
           <t>F-4</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1936,6 +2154,12 @@
       <c r="I33" s="3" t="inlineStr">
         <is>
           <t>D-10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
